--- a/tests/fixtures/extract_corpus_v2/dev/bundle_vv40_cht_012/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_vv40_cht_012/extracted.xlsx
@@ -490,6 +490,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -565,21 +570,6 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
-    <comment ref="A7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="B7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="D7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -691,11 +681,6 @@
       </text>
     </comment>
     <comment ref="F5" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="G5" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1423,12 +1408,12 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>Conjugate heat transfer CFD model for predicting peak die-cap temperatures in inverter cold plate assembly</t>
+          <t>Conjugate heat transfer model for inverter cold plate and SiC MOSFET board stack thermal management</t>
         </is>
       </c>
       <c r="C3" s="39" t="inlineStr">
         <is>
-          <t>Ansys Fluent 2023R2 CHT model of a two-pass aluminum cold plate bonded to a copper spreader under four SiC MOSFET modules, used to predict hottest die-cap temperature and coolant temperature rise under 180 W load at 2.0 L/min 50/50 water-glycol at 25 C inlet. Intended for thermal margin assessment and cooling geometry decisions through EVT and potentially DVT.</t>
+          <t>Steady-state CFD/CHT model (Ansys Fluent 2023R2, SST k-ω) of a two-pass aluminum cold plate bonded to a copper spreader under four SiC MOSFET modules, used to predict hottest die-cap temperature and coolant temperature rise under 180 W load at 2.0 L/min, 25 C inlet. Intended to support EVT build decisions with a 5–7 C guard band; DVT sign-off not yet supported.</t>
         </is>
       </c>
       <c r="D3" s="39" t="inlineStr">
@@ -1466,9 +1451,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="39" t="inlineStr">
+        <is>
+          <t>report.md</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -2064,7 +2049,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>Peak Die-Cap Temperature Prediction Accuracy</t>
+          <t>Hottest die-cap temperature prediction within acceptable error for EVT thermal margin</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
@@ -2074,7 +2059,7 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>Model must predict hottest die-cap temperature within an acceptable margin to support EVT thermal margin decisions; current guard band set at 5-7 C above CFD prediction pending model closure</t>
+          <t>Model must predict peak die-cap temperature sufficiently accurately to support EVT thermal decisions; current acceptance criterion is CFD result plus a 7 C guard band, with residual model bias documented and bounded.</t>
         </is>
       </c>
       <c r="E3" s="22" t="inlineStr">
@@ -2091,18 +2076,18 @@
     <row r="4" ht="15" customHeight="1" s="18">
       <c r="A4" s="41" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="B4" s="41" t="inlineStr">
         <is>
-          <t>Coolant Temperature Rise Prediction</t>
+          <t>Ansys Fluent 2023R2 CHT Model — M5 Cold Plate</t>
         </is>
       </c>
       <c r="C4" s="24" t="n"/>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>Model must predict coolant outlet temperature rise adequately for energy balance validation against bench measurements (target: agree with measured 3.6±0.2 C rise)</t>
+          <t>Pressure-based coupled solver with SST k-ω turbulence, poly-hexcore mesh (8.3M fluid + 2.1M solid cells), temperature-dependent material properties, steady-state baseline run R07.</t>
         </is>
       </c>
       <c r="E4" s="33" t="n"/>
@@ -2111,18 +2096,18 @@
     <row r="5" ht="15" customHeight="1" s="18">
       <c r="A5" s="41" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Dataset</t>
         </is>
       </c>
       <c r="B5" s="41" t="inlineStr">
         <is>
-          <t>Ansys Fluent 2023R2 CHT Model (Run R07 baseline)</t>
+          <t>M5 Coupon Bench Thermal Test Data</t>
         </is>
       </c>
       <c r="C5" s="24" t="n"/>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>Pressure-based coupled solver, SST k-omega turbulence, poly-hexcore mesh (8.3M fluid + 2.1M solid cells), steady-state, temperature-dependent material properties, modeling cold plate and SiC MOSFET module stack</t>
+          <t>Measured hottest cap temperature (68.5±0.7 C) and coolant rise (3.6±0.2 C) from M5 coupon on thermal stand at 2.0 L/min, 25 C inlet, 180 W; T-type microbead sensors and IR spot check.</t>
         </is>
       </c>
       <c r="E5" s="33" t="n"/>
@@ -2136,35 +2121,23 @@
       </c>
       <c r="B6" s="41" t="inlineStr">
         <is>
-          <t>M5 Coupon Bench Thermal Measurements</t>
+          <t>TIM Thickness Metrology Report</t>
         </is>
       </c>
       <c r="C6" s="24" t="n"/>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>Experimental measurements from M5 thermal stand: hottest cap 68.5±0.7 C, coolant rise 3.6±0.2 C at 2.0 L/min, 25 C inlet, 180 W; T-type microbead thermocouples and IR spot check</t>
+          <t>Gage-pin measurements of TIM-1 thickness distribution showing 0.07–0.12 mm spread across M5 prototype; used for back-of-envelope sensitivity (+0.05 mm ≈ +1.1 C).</t>
         </is>
       </c>
       <c r="E6" s="33" t="n"/>
       <c r="F6" s="33" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1" s="18">
-      <c r="A7" s="41" t="inlineStr">
-        <is>
-          <t>Dataset</t>
-        </is>
-      </c>
-      <c r="B7" s="41" t="inlineStr">
-        <is>
-          <t>TIM Thickness Metrology Report</t>
-        </is>
-      </c>
+      <c r="A7" s="24" t="n"/>
+      <c r="B7" s="24" t="n"/>
       <c r="C7" s="24" t="n"/>
-      <c r="D7" s="41" t="inlineStr">
-        <is>
-          <t>Gage pin measurements of TIM-1 thickness showing 0.07-0.12 mm spread vs 0.10 mm nominal; Monte Carlo UQ on this distribution was deferred</t>
-        </is>
-      </c>
+      <c r="D7" s="33" t="n"/>
       <c r="E7" s="33" t="n"/>
       <c r="F7" s="33" t="n"/>
     </row>
@@ -2304,7 +2277,7 @@
     <row r="3" ht="32.8" customHeight="1" s="18">
       <c r="A3" s="39" t="inlineStr">
         <is>
-          <t>Peak Die-Cap Temperature Comparison (R07 vs Bench)</t>
+          <t>Mesh Convergence Study</t>
         </is>
       </c>
       <c r="B3" s="39" t="inlineStr">
@@ -2319,12 +2292,12 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>Baseline steady-state CHT run R07 predicted hottest cap temperature of 63.2 C compared to measured 68.5±0.7 C on M5 coupon bench at identical nominal conditions</t>
+          <t>Three mesh levels (5.2M / 8.3M / 14.7M cells) evaluated for hottest-cap temperature sensitivity. Hottest-cap prediction shifted 1.2% across coarse to fine. GCI quoted at 0.5%, but monotonicity assumption is undermined by wall y+ increase in U-turn region on finest mesh due to blocking artifact.</t>
         </is>
       </c>
       <c r="E3" s="39" t="inlineStr">
         <is>
-          <t>M5 bench microbead thermocouple measurement (68.5±0.7 C)</t>
+          <t>Coarser mesh levels; Richardson extrapolation / GCI estimate</t>
         </is>
       </c>
       <c r="F3" s="39" t="inlineStr">
@@ -2334,24 +2307,24 @@
       </c>
       <c r="G3" s="39" t="inlineStr">
         <is>
-          <t>Experimental measurement uncertainty quoted (±0.7 C); CFD model uncertainty not formally quantified</t>
+          <t>Grid Convergence Index (GCI), Richardson extrapolation (noted as unreliable due to non-monotonicity)</t>
         </is>
       </c>
       <c r="H3" s="39" t="inlineStr">
         <is>
-          <t>~8% underprediction of peak temperature (5.3 C absolute deviation); earlier claimed 3% using non-representative TIM conductivity nudge</t>
+          <t>1.2% variation coarse-to-fine; GCI quoted 0.5% (validity uncertain)</t>
         </is>
       </c>
       <c r="I3" s="42" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Inconclusive</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="18">
       <c r="A4" s="41" t="inlineStr">
         <is>
-          <t>Coolant Temperature Rise Comparison (R07 vs Bench)</t>
+          <t>Peak Die-Cap Temperature Comparison to Bench Data</t>
         </is>
       </c>
       <c r="B4" s="41" t="inlineStr">
@@ -2362,12 +2335,12 @@
       <c r="C4" s="33" t="n"/>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>Baseline run R07 predicted coolant temperature rise of 3.2 C compared to measured 3.6±0.2 C at same nominal conditions</t>
+          <t>Baseline steady run R07 predicted 63.2 C hottest cap vs. measured 68.5±0.7 C; coolant rise 3.2 C vs. 3.6±0.2 C measured. Model is optimistic by approximately 5.3 C (~8%) on peak temperature. An earlier slide deck claimed 3% agreement using a non-standard TIM conductivity (3.8 vs. 3.0 W/m-K), which was not carried forward.</t>
         </is>
       </c>
       <c r="E4" s="41" t="inlineStr">
         <is>
-          <t>M5 bench coolant outlet thermocouple measurement (3.6±0.2 C)</t>
+          <t>M5 coupon bench thermal test data</t>
         </is>
       </c>
       <c r="F4" s="41" t="inlineStr">
@@ -2377,12 +2350,12 @@
       </c>
       <c r="G4" s="41" t="inlineStr">
         <is>
-          <t>Experimental uncertainty quoted (±0.2 C)</t>
+          <t>Experimental measurement uncertainty reported (±0.7 C peak, ±0.2 C rise); model sensitivity studies (flow rate ±0.2 L/min, turbulence intensity, TIM thickness back-of-envelope)</t>
         </is>
       </c>
       <c r="H4" s="41" t="inlineStr">
         <is>
-          <t>11% underprediction of coolant rise (0.4 C absolute deviation); outside measurement uncertainty band</t>
+          <t>8% low on peak cap temperature; 11% low on coolant rise</t>
         </is>
       </c>
       <c r="I4" s="42" t="inlineStr">
@@ -2394,7 +2367,7 @@
     <row r="5" ht="15" customHeight="1" s="18">
       <c r="A5" s="41" t="inlineStr">
         <is>
-          <t>Mesh Convergence / Sensitivity Study</t>
+          <t>Pressure Drop Correlation Check</t>
         </is>
       </c>
       <c r="B5" s="41" t="inlineStr">
@@ -2405,12 +2378,12 @@
       <c r="C5" s="33" t="n"/>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>Three mesh levels tested: 5.2M, 8.3M, 14.7M cells (fluid+solid). Hottest-cap prediction shifted 1.2% across levels. GCI quoted as 0.5% but monotonicity assumption is noted as shaky due to y+ increase on finest mesh in U-turn region from blocking artifact.</t>
+          <t>Predicted pressure drop compared against straight-channel turbulent correlation; agreement within 4%.</t>
         </is>
       </c>
       <c r="E5" s="41" t="inlineStr">
         <is>
-          <t>Richardson extrapolation / GCI methodology (analytical)</t>
+          <t>Analytical turbulent straight-channel correlation</t>
         </is>
       </c>
       <c r="F5" s="41" t="inlineStr">
@@ -2418,26 +2391,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="G5" s="41" t="inlineStr">
-        <is>
-          <t>GCI quoted but flagged as unreliable due to non-monotonic y+ behavior</t>
-        </is>
-      </c>
+      <c r="G5" s="33" t="n"/>
       <c r="H5" s="41" t="inlineStr">
         <is>
-          <t>1.2% variation across mesh levels; GCI 0.5% (reliability uncertain)</t>
+          <t>4% error vs. correlation</t>
         </is>
       </c>
       <c r="I5" s="42" t="inlineStr">
         <is>
-          <t>Inconclusive</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="18">
       <c r="A6" s="41" t="inlineStr">
         <is>
-          <t>Pressure Drop Verification vs Correlation</t>
+          <t>Pipe-Heating Sanity Case</t>
         </is>
       </c>
       <c r="B6" s="41" t="inlineStr">
@@ -2448,12 +2417,12 @@
       <c r="C6" s="33" t="n"/>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>Pressure drop predicted by CFD compared against straight-channel turbulent correlation; agreement within 4%</t>
+          <t>Convective pipe-heating case from White textbook run as a code sanity check; 0.3% error. Relevance to the strongly 3D corner flows in the actual geometry is acknowledged as limited.</t>
         </is>
       </c>
       <c r="E6" s="41" t="inlineStr">
         <is>
-          <t>Analytical turbulent straight-channel correlation</t>
+          <t>White textbook analytical solution for convective pipe heating</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
@@ -2464,7 +2433,7 @@
       <c r="G6" s="33" t="n"/>
       <c r="H6" s="41" t="inlineStr">
         <is>
-          <t>Within 4%</t>
+          <t>0.3% error</t>
         </is>
       </c>
       <c r="I6" s="42" t="inlineStr">
@@ -2476,7 +2445,7 @@
     <row r="7" ht="15" customHeight="1" s="18">
       <c r="A7" s="41" t="inlineStr">
         <is>
-          <t>Pipe Heating Sanity Case (White)</t>
+          <t>Transient Recirculation Check (R10)</t>
         </is>
       </c>
       <c r="B7" s="41" t="inlineStr">
@@ -2487,12 +2456,12 @@
       <c r="C7" s="33" t="n"/>
       <c r="D7" s="41" t="inlineStr">
         <is>
-          <t>Pipe-heating convective heat-up benchmark from White's textbook run against CFD solver; 0.3% error. Noted as having limited relevance to strongly 3D corner flows in the actual geometry.</t>
+          <t>Quick transient run (R10, 0.1 s steps, 3 s total) revealed 1–1.5 C oscillation in wake of U-turn bend. Results not propagated into baseline. Steady-state assumption for baseline not fully validated.</t>
         </is>
       </c>
       <c r="E7" s="41" t="inlineStr">
         <is>
-          <t>White textbook analytical/benchmark solution</t>
+          <t>Steady-state baseline</t>
         </is>
       </c>
       <c r="F7" s="41" t="inlineStr">
@@ -2503,12 +2472,12 @@
       <c r="G7" s="33" t="n"/>
       <c r="H7" s="41" t="inlineStr">
         <is>
-          <t>0.3% error</t>
+          <t>1–1.5 C oscillation amplitude</t>
         </is>
       </c>
       <c r="I7" s="42" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Inconclusive</t>
         </is>
       </c>
     </row>
@@ -2727,12 +2696,12 @@
       </c>
       <c r="E5" s="42" t="inlineStr">
         <is>
-          <t>Commercial solver with documented QA; version controlled inputs</t>
+          <t>Commercial solver with documented QA, version control of case files for all runs.</t>
         </is>
       </c>
       <c r="F5" s="41" t="inlineStr">
         <is>
-          <t>Ansys Fluent 2023R2 is a commercial solver with implied vendor QA. Case files for R03-R10 are version controlled on Git (tag m5_cht_ev1). However, R01-R02 original case files are lost (were on analyst's laptop during travel; only reproduced results archived). No explicit mention of regression testing, ISO certification process, or formal SQA documentation referenced. Single-precision run R06 was tested but excluded from rollups.</t>
+          <t>Ansys Fluent 2023R2 is a commercial solver with implied vendor QA, but no explicit certification documentation or regression test suite is cited. Case files for R03–R10 are version-controlled on Git (tag m5_cht_ev1). R01–R02 case files were lost (laptop during travel) and only reproduced results are available — a traceability gap. No ISO or formal SQA process documented.</t>
         </is>
       </c>
       <c r="G5" s="41" t="inlineStr">
@@ -2753,19 +2722,19 @@
         </is>
       </c>
       <c r="C6" s="41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="41" t="n">
         <v>2</v>
       </c>
       <c r="E6" s="42" t="inlineStr">
         <is>
-          <t>Benchmarks against analytical solutions covering relevant physics</t>
+          <t>Code correctly solves governing equations, demonstrated via benchmark or analytical comparison.</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
         <is>
-          <t>Two benchmark comparisons performed: (1) straight-channel turbulent pressure drop correlation, within 4%; (2) pipe-heating sanity case from White, 0.3% error. Both are simple 1D/straight-channel problems. The memo explicitly notes limited relevance of these to the strongly 3D corner flows and U-turn geometry of the actual device. No manufactured solution or more demanding 3D benchmark was performed. SST k-omega model with curvature correction off is not verified against a curved-flow benchmark.</t>
+          <t>Pipe-heating sanity case from White yielded 0.3% error against an analytical solution. Pressure drop checked against a straight-channel turbulent correlation to within 4%. These are simple benchmarks; no Method of Manufactured Solutions or more rigorous code verification is documented. Relevance of benchmarks to the 3D corner-flow geometry is explicitly noted as limited.</t>
         </is>
       </c>
       <c r="G6" s="41" t="inlineStr">
@@ -2793,12 +2762,12 @@
       </c>
       <c r="E7" s="42" t="inlineStr">
         <is>
-          <t>Monotonic mesh convergence with reliable GCI estimate</t>
+          <t>Monotone mesh refinement with valid GCI estimate below an acceptable threshold.</t>
         </is>
       </c>
       <c r="F7" s="41" t="inlineStr">
         <is>
-          <t>Three mesh levels tested (5.2M, 8.3M, 14.7M cells). Peak temperature varies 1.2% across levels; GCI quoted as 0.5%. However, the memo explicitly flags that monotonicity assumption is violated: the finest mesh shows increased y+ in U-turn region due to a blocking artifact. The near-wall target y+~1 for SST is not achieved (actual y+ 15-30 along mid-channel walls). Transient oscillations (1-1.5 C) were observed but not incorporated into the steady baseline. Action to rebuild finest mesh is open.</t>
+          <t>Three mesh levels were run (5.2M / 8.3M / 14.7M cells); hottest-cap varied 1.2%; GCI quoted at 0.5%. However, the finest mesh exhibited increased wall y+ in the U-turn region due to a blocking artifact, violating the monotonicity assumption required for GCI validity. The analyst explicitly flags the GCI as unreliable and recommends rebuilding the finest mesh. Achieved level is therefore limited to 2.</t>
         </is>
       </c>
       <c r="G7" s="41" t="inlineStr">
@@ -2826,12 +2795,12 @@
       </c>
       <c r="E8" s="42" t="inlineStr">
         <is>
-          <t>Converged residuals and stable key monitor quantities</t>
+          <t>Residuals reach target thresholds and key monitors converge stably.</t>
         </is>
       </c>
       <c r="F8" s="41" t="inlineStr">
         <is>
-          <t>Energy residuals &lt;1e-6, others &lt;1e-4 in most runs. Key monitors (hottest die cap, coolant outlet T) flattened to within 0.2 C over last 2k iterations in most runs. Exception noted: Run R08 showed 0.8 C drift in hottest node over last 500 iterations suggesting a slow recirculation mode. Double precision used throughout except R06 (single precision, excluded from rollups, within 0.3 C of double precision result). Convergence monitoring is documented and adequate for most runs.</t>
+          <t>Energy residuals &lt;1e-6, momentum/continuity &lt;1e-4. Key monitors (hottest die cap, outlet T) flattened to within 0.2 C over 2k iterations for most runs. Exception: R08 hottest node drifted ~0.8 C over last 500 iters while residuals continued to decrease, suggesting a slow recirculation mode — this run was noted but the issue was not resolved for all cases. Double precision used throughout except R06 (not included in rollups). Overall convergence behavior is mostly adequate with a documented exception.</t>
         </is>
       </c>
       <c r="G8" s="41" t="inlineStr">
@@ -2855,16 +2824,16 @@
         <v>3</v>
       </c>
       <c r="D9" s="41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" s="42" t="inlineStr">
         <is>
-          <t>Independent review of model setup, BCs, and post-processing</t>
+          <t>Independent review of model setup, boundary conditions verified, mesh quality checked.</t>
         </is>
       </c>
       <c r="F9" s="41" t="inlineStr">
         <is>
-          <t>Multiple setup errors identified in the memo: R01-R02 used wrong fixed viscosity (corrected in later runs); R09 inadvertently included surface-to-surface radiation; turbulence intensity was inconsistently set (5% legacy template vs 10% matching vendor data); a slide deck previously reported a misleading 3% error using a non-representative TIM conductivity nudge. Peer review was performed by S. Ng, but the memo explicitly notes this is not fully independent (S. Ng also created the plate CAD). The combination of multiple discovered errors and non-independent review yields minimal confidence against use error.</t>
+          <t>Peer review was performed by S. Ng, but S. Ng also created the plate CAD — not a fully independent reviewer. Several setup errors were discovered during the study: R01–R02 used incorrect fixed viscosity (1.5e-3 Pa·s); R09 inadvertently included surface-to-surface radiation; inlet turbulence intensity was set to 5% (legacy template) instead of vendor-specified 10% in early runs. These errors indicate insufficient setup controls. Corrective actions identified but not yet completed.</t>
         </is>
       </c>
       <c r="G9" s="41" t="inlineStr">
@@ -2892,12 +2861,12 @@
       </c>
       <c r="E10" s="42" t="inlineStr">
         <is>
-          <t>Governing equations and turbulence model justified for the flow regime; known limitations documented</t>
+          <t>Governing physics and turbulence model selection justified; known limitations documented.</t>
         </is>
       </c>
       <c r="F10" s="41" t="inlineStr">
         <is>
-          <t>SST k-omega selected for coolant with curvature correction off. Radiation excluded from baseline (sealed enclosure). Orthotropic equivalent for board stack is documented with property values. The memo notes curvature correction off is potentially inappropriate for the U-turn geometry; the radiation inconsistency (R09 lowered predicted peak despite nominally non-participating enclosure) is flagged but unresolved. Steady-state assumption is noted as approximate given 1-1.5 C transient oscillations. Governing equations are standard for CHT but the selection rationale and known limitations are only informally documented in this memo.</t>
+          <t>SST k-ω with curvature correction off is used. The choice of turbulence model is stated but not formally justified against alternatives. Steady-state assumption is partially challenged by the transient check (R10) showing 1–1.5 C oscillations. Radiation is off in baseline but was accidentally included in R09 with a ~0.4 C effect, raising questions about enclosure assumptions. Orthotropic board conductivity values are stated without sourcing. Limitations are partially documented but not systematically addressed.</t>
         </is>
       </c>
       <c r="G10" s="41" t="inlineStr">
@@ -2925,12 +2894,12 @@
       </c>
       <c r="E11" s="42" t="inlineStr">
         <is>
-          <t>Material properties and BCs well-characterized with uncertainties; geometry from metrology</t>
+          <t>Material properties and boundary conditions traceable to measurements or vendor data; input uncertainties characterized.</t>
         </is>
       </c>
       <c r="F11" s="41" t="inlineStr">
         <is>
-          <t>Temperature-dependent coolant properties from NIST tables; solid conductivities temperature-dependent. TIM conductivity uses vendor nominal (3.0 W/m-K) but a prior run nudged it to 3.8 W/m-K to improve match, indicating uncertainty. TIM thickness from gage pin metrology (0.07-0.12 mm spread) but Monte Carlo UQ was deferred. Inlet turbulence intensity was inconsistently set between runs. Flow rate sensitivity documented (±0.2 L/min → ±1.9 C). Contact resistance at spreader/plate bond not explicitly modeled. R01-R02 viscosity error indicates input control gaps.</t>
+          <t>Coolant properties from NIST tables; solid conductivities are temperature-dependent but sources not fully cited. TIM conductivity nominal from vendor sheet (3.0 W/m-K) but a prior run used a non-standard value (3.8 W/m-K) without clear justification. TIM thickness nominally set to single values (0.10 / 0.08 mm) despite metrology showing 0.07–0.12 mm spread; Monte Carlo of this was deferred. Flow rate from Sorensen S300 pump at 2.0 L/min; turbulence intensity inconsistency (5% vs. 10%) was present across runs. Board orthotropic conductivity values stated without measurement source. Input uncertainties are partially identified but not systematically propagated.</t>
         </is>
       </c>
       <c r="G11" s="41" t="inlineStr">
@@ -2958,12 +2927,12 @@
       </c>
       <c r="E12" s="42" t="inlineStr">
         <is>
-          <t>Representative test article with documented configuration</t>
+          <t>Test article is representative; sample count and production-representativeness documented.</t>
         </is>
       </c>
       <c r="F12" s="41" t="inlineStr">
         <is>
-          <t>Single M5 prototype coupon tested on thermal stand. The memo describes it as the M5 coupon (prototype stage, not production-representative). No multiple specimens or statistical characterization across samples. The test article configuration (TIM thickness, bond quality) is partially characterized by gage pin metrology but variability not fully propagated. Single coupon is adequate for a prototype stage but limits statistical inference.</t>
+          <t>A single M5 prototype coupon was tested on the thermal stand. The coupon is described as the M5 prototype; no information on number of replicates, production-representativeness, or statistical characterization of unit-to-unit variation is provided. Single-specimen testing is common at this stage but limits statistical confidence.</t>
         </is>
       </c>
       <c r="G12" s="41" t="inlineStr">
@@ -2984,19 +2953,19 @@
         </is>
       </c>
       <c r="C13" s="41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="41" t="n">
         <v>3</v>
       </c>
       <c r="E13" s="42" t="inlineStr">
         <is>
-          <t>Calibrated instruments; controlled and documented test conditions</t>
+          <t>Calibrated instrumentation, controlled environment, documented measurement uncertainty.</t>
         </is>
       </c>
       <c r="F13" s="41" t="inlineStr">
         <is>
-          <t>Test conditions specified: 2.0 L/min from Sorensen S300 pump, 25 C inlet, 180 W. Measurement instrumentation documented: T-type microbead thermocouples in each module cap with uncertainty ±0.7 C, IR spot check through window. Coolant rise measurement uncertainty ±0.2 C. Flow rate sensitivity characterized. Conditions are well-specified and match the CFD nominal inputs. No explicit calibration certificates referenced but instrument types and uncertainties are stated.</t>
+          <t>T-type microbead thermocouples at each module cap and IR spot check used. Coolant supplied by Sorensen S300 pump at controlled 2.0 L/min, 25 C inlet. Measurement uncertainties are reported: ±0.7 C on peak cap temperature, ±0.2 C on coolant rise. Test conditions (flow rate, inlet temperature, power) match simulation inputs. No formal test standard (e.g., ASTM) cited, and environmental conditions (ambient, enclosure) are not fully described, but basic instrumentation uncertainty is quantified.</t>
         </is>
       </c>
       <c r="G13" s="41" t="inlineStr">
@@ -3024,12 +2993,12 @@
       </c>
       <c r="E14" s="42" t="inlineStr">
         <is>
-          <t>CFD boundary conditions matched to measured test conditions with uncertainty propagation</t>
+          <t>Model boundary conditions match experimental conditions; input parameter comparison documented with uncertainty propagation.</t>
         </is>
       </c>
       <c r="F14" s="41" t="inlineStr">
         <is>
-          <t>Nominal CFD inputs match bench conditions (2.0 L/min, 25 C inlet, 180 W, same geometry). However, turbulence intensity mismatch between runs (5% vs 10%) was not resolved until sensitivity study, adding 0.6 C. TIM thickness in model uses single nominal value despite measured spread of 0.07-0.12 mm. Fixed viscosity error in R01-R02 (corrected later). No formal input uncertainty propagation from test measurements to CFD inputs; back-of-envelope estimates provided for some parameters but not systematically.</t>
+          <t>Nominal test conditions (2.0 L/min, 25 C inlet, 180 W) are replicated in the simulation. However, inlet turbulence intensity inconsistency across runs (5% vs. 10%) means the baseline R07 may not precisely match measured pump conditions. TIM thickness is set to nominal values rather than the measured distribution. Viscosity errors in early runs (R01–R02) represent input mismatches that were corrected. Sensitivity of peak temperature to flow rate (±1.9 C per ±0.2 L/min) is quantified but formal input uncertainty propagation was not completed.</t>
         </is>
       </c>
       <c r="G14" s="41" t="inlineStr">
@@ -3057,12 +3026,12 @@
       </c>
       <c r="E15" s="42" t="inlineStr">
         <is>
-          <t>Quantitative comparison of model predictions to measurements with uncertainty bands; multiple QoIs</t>
+          <t>Quantitative comparison of predicted vs. measured QoIs with uncertainty bands; multiple comparison points.</t>
         </is>
       </c>
       <c r="F15" s="41" t="inlineStr">
         <is>
-          <t>Two QoIs compared: peak die-cap temperature (CFD 63.2 C vs measured 68.5±0.7 C, ~8% underprediction) and coolant temperature rise (CFD 3.2 C vs measured 3.6±0.2 C, ~11% underprediction). Both show systematic underprediction. Experimental uncertainties are quoted but CFD prediction uncertainty is not formally quantified. The memo notes a prior misleading 3% claim using a non-representative parameter nudge. Sensitivity studies provide partial uncertainty information. No statistical validation metrics (e.g., coverage intervals, area validation metrics) applied.</t>
+          <t>Baseline R07 predicts 63.2 C vs. 68.5±0.7 C measured (~8% low) and 3.2 C vs. 3.6±0.2 C coolant rise (~11% low). Sensitivity studies for flow rate and turbulence intensity are reported. However, only two scalar QoIs are compared (peak cap T and coolant rise); no spatial temperature distributions or multi-point comparisons are reported. Experimental uncertainty is quantified but model uncertainty bands are not formally propagated. An earlier misleading claim of 3% agreement is noted and retracted.</t>
         </is>
       </c>
       <c r="G15" s="41" t="inlineStr">
@@ -3086,16 +3055,16 @@
         <v>3</v>
       </c>
       <c r="D16" s="41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" s="42" t="inlineStr">
         <is>
-          <t>QoIs directly reflect thermal safety margins for MOSFET junctions; measurable computationally and experimentally</t>
+          <t>Model QoIs directly correspond to the thermal safety and performance concerns; measurable both computationally and experimentally.</t>
         </is>
       </c>
       <c r="F16" s="41" t="inlineStr">
         <is>
-          <t>Peak die-cap temperature directly relates to MOSFET junction temperature and thermal margin, which is the primary design concern for the inverter. Coolant temperature rise is directly relevant to system energy balance. Both QoIs are measured experimentally (thermocouples and IR) and directly output by the CHT simulation. The QoIs are well-chosen for the intended use (EVT/DVT thermal sign-off decisions). Flow rate sensitivity also computed.</t>
+          <t>The primary QoI — hottest die-cap temperature — directly corresponds to the thermal reliability limit for SiC MOSFETs and is both predicted by the model and measured on the bench. Coolant temperature rise is a secondary QoI relevant to system-level thermal budget. Both QoIs are clearly relevant to the EVT thermal margin decision. The QoIs are appropriate and well-chosen for the COU.</t>
         </is>
       </c>
       <c r="G16" s="41" t="inlineStr">
@@ -3123,12 +3092,12 @@
       </c>
       <c r="E17" s="42" t="inlineStr">
         <is>
-          <t>Validation conditions match intended operating envelope; same geometry, same physics regime, same load cases</t>
+          <t>Validation test conditions match intended use geometry, operating range, and physics regime.</t>
         </is>
       </c>
       <c r="F17" s="41" t="inlineStr">
         <is>
-          <t>Validation performed on the M5 prototype coupon at a single operating point (2.0 L/min, 25 C inlet, 180 W, steady state) matching the primary COU condition. Geometry is the actual device (not a surrogate). However, several gaps exist: only one operating point validated (no variation in flow rate, inlet temperature, or load distribution tested experimentally); transient behavior observed in CFD but not validated; the bench article is a prototype coupon not a production part; multiple open modeling issues (mesh, wall treatment, radiation BCs, TIM characterization) reduce confidence that the validated model represents the intended DVT/production COU.</t>
+          <t>Validation was performed on the M5 prototype coupon at the nominal operating point (2.0 L/min, 25 C, 180 W), which matches the intended COU. Geometry is production-representative at this prototype stage. However, only a single operating point was validated; off-nominal conditions (e.g., reduced flow, elevated inlet temperature, partial load) were not tested. Transient behavior relevant to real drive cycles was not validated. The model is explicitly flagged as not ready for DVT sign-off, indicating known gaps in coverage of the full COU envelope.</t>
         </is>
       </c>
       <c r="G17" s="41" t="inlineStr">
@@ -3217,7 +3186,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>The CHT model is accepted for the limited purpose of supporting EVT builds with a mandatory 7 C thermal guard band applied above CFD predictions. The model shows systematic underprediction of ~5-8% on peak die-cap temperature and ~11% on coolant rise relative to M5 bench measurements. Multiple modeling issues have been identified and documented: non-monotonic mesh refinement behavior, unresolved wall y+ targets, inconsistent turbulence inlet conditions, deferred TIM thickness UQ, unresolved radiation BC inconsistency, and non-independent peer review. Acceptance is contingent on: (1) the 7 C guard band being applied for all EVT decisions; (2) the six open action items in the memo being closed before DVT geometry lock; (3) Run R07 not being used as-is for DVT sign-off per analyst recommendation. The model is explicitly NOT accepted for DVT sign-off in its current state.</t>
+          <t>The CHT model is accepted for the limited purpose of supporting EVT build decisions with a mandatory 7 C thermal guard band applied to all R07 predictions. The model is not accepted for DVT cooling geometry lock-off. Acceptance is conditioned on: (1) application of the 7 C guard band to account for the documented ~8% optimistic bias; (2) completion of the six open actions identified by the analyst before any DVT gate, specifically: rebuilding the finest mesh to achieve y+&lt;1 in hotspot regions and rerunning the refinement triplet; locking inlet turbulence intensity to 10% and rebaselining; running a resolved transient to quantify recirculation-driven temperature fluctuations; calibrating TIM thickness inputs from the metrology distribution; removing or properly characterizing radiation boundary conditions; and archiving R01–R02 case files or formally retiring those runs. The residual 8% temperature underprediction, non-monotone mesh refinement, partially independent review, and multiple corrected setup errors collectively preclude higher-confidence use at this time.</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
@@ -3227,7 +3196,7 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>R. Patel (CHT Analyst, recommendation); Mira (Thermal Lead, addressee)</t>
+          <t>R. Patel</t>
         </is>
       </c>
       <c r="E3" s="39" t="inlineStr">
